--- a/harga_sembako.xlsx
+++ b/harga_sembako.xlsx
@@ -2931,7 +2931,7 @@
         <v>134000</v>
       </c>
       <c r="R32" s="3" t="n">
-        <v>202900</v>
+        <v>202000</v>
       </c>
       <c r="S32" s="3" t="n">
         <v>3100</v>
